--- a/Documentation/Week 5/Booked Hours/Booked_Hours_Dylan.xlsx
+++ b/Documentation/Week 5/Booked Hours/Booked_Hours_Dylan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 5/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{C839D0D7-89B3-4B1F-A7FA-FAF46048CC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C795530C-968A-4C96-AFBC-1D9DD57B8B4F}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{C839D0D7-89B3-4B1F-A7FA-FAF46048CC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D698C389-00D4-4357-BF47-31D0CCA46B68}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
   <si>
     <r>
       <t xml:space="preserve">CITS3200 Project Billed Hours Record for &lt;Dylan Hu&gt;
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tested and debugged person identification prototype </t>
+  </si>
+  <si>
+    <t>Filling in team timesheet</t>
   </si>
 </sst>
 </file>
@@ -802,7 +805,7 @@
     <col min="6" max="6" width="64.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.6328125" style="1"/>
-    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="0.36328125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
@@ -1294,7 +1297,7 @@
         <v>18</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" ref="G17" si="5">IF(I17&gt;0,I17,IF(I17=0, " ", "ERROR"))</f>
+        <f t="shared" ref="G17:G18" si="5">IF(I17&gt;0,I17,IF(I17=0, " ", "ERROR"))</f>
         <v>0.49999999988358468</v>
       </c>
       <c r="H17" s="1">
@@ -1307,21 +1310,35 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="G18" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H18" s="1" t="str">
+      <c r="A18" s="1">
+        <v>5</v>
+      </c>
+      <c r="B18" s="4">
+        <v>44793</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.93055555555555558</v>
+      </c>
+      <c r="D18" s="4">
+        <v>44793</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.94097222222222221</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="6">
+        <f t="shared" si="5"/>
+        <v>0.24999999994179234</v>
+      </c>
+      <c r="H18" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>17.749999999534339</v>
       </c>
       <c r="I18" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>((D18+E18)-(B18+C18))*24</f>
+        <v>0.24999999994179234</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
